--- a/therapist_forms/004_couples_questionnaire--therapist_forms.xlsx
+++ b/therapist_forms/004_couples_questionnaire--therapist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How satisfied are you with your current relationship?</t>
+          <t>Relationship Satisfaction Scale</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How long have you been in your current relationship?</t>
+          <t>Relationship Duration 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is the current relationship status?</t>
+          <t>Relationship Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How satisfied are you with your current relationship?</t>
+          <t>Relationship Satisfaction 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What are your expectations for your relationship?</t>
+          <t>Relationship Expectations 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What are some common challenges that prevent you from communicating effectively with your partner?</t>
+          <t>Relationship Challenges 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What happened to your last relationship?</t>
+          <t>Relationship History 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
